--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003 REV0.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,6 +146,11 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -488,10 +493,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3218,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3450,15 +3455,24 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
+      <c r="B10" s="59" t="n"/>
       <c r="C10" s="59" t="n"/>
       <c r="D10" s="59" t="n"/>
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
@@ -3466,15 +3480,24 @@
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>HD-REJ-001</t>
-        </is>
-      </c>
+      <c r="B11" s="61" t="n"/>
       <c r="C11" s="61" t="n"/>
       <c r="D11" s="61" t="n"/>
       <c r="E11" s="61" t="n"/>
       <c r="F11" s="61" t="n"/>
+      <c r="G11" s="61" t="n"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="I11" s="60" t="inlineStr">
+        <is>
+          <t>HD-REJ-001</t>
+        </is>
+      </c>
+      <c r="J11" s="61" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="61" t="n"/>
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
@@ -3482,15 +3505,24 @@
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="B12" s="61" t="n"/>
       <c r="C12" s="61" t="n"/>
       <c r="D12" s="61" t="n"/>
       <c r="E12" s="61" t="n"/>
       <c r="F12" s="61" t="n"/>
+      <c r="G12" s="61" t="n"/>
+      <c r="H12" s="61" t="n"/>
+      <c r="I12" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="61" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="61" t="n"/>
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
@@ -3498,15 +3530,24 @@
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+      <c r="B13" s="61" t="n"/>
       <c r="C13" s="61" t="n"/>
       <c r="D13" s="61" t="n"/>
       <c r="E13" s="61" t="n"/>
       <c r="F13" s="61" t="n"/>
+      <c r="G13" s="61" t="n"/>
+      <c r="H13" s="61" t="n"/>
+      <c r="I13" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J13" s="61" t="n"/>
+      <c r="K13" s="61" t="n"/>
+      <c r="L13" s="61" t="n"/>
+      <c r="M13" s="61" t="n"/>
+      <c r="N13" s="61" t="n"/>
+      <c r="O13" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="60" t="inlineStr">
@@ -3514,15 +3555,24 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
-        <is>
-          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
-        </is>
-      </c>
+      <c r="B14" s="61" t="n"/>
       <c r="C14" s="61" t="n"/>
       <c r="D14" s="61" t="n"/>
       <c r="E14" s="61" t="n"/>
       <c r="F14" s="61" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
+        </is>
+      </c>
+      <c r="J14" s="61" t="n"/>
+      <c r="K14" s="61" t="n"/>
+      <c r="L14" s="61" t="n"/>
+      <c r="M14" s="61" t="n"/>
+      <c r="N14" s="61" t="n"/>
+      <c r="O14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="60" t="inlineStr">
@@ -3530,15 +3580,24 @@
           <t>Etiqueta de equipo</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
-        <is>
-          <t>REJ-001 a REJ-003 (rejillas de exfiltración)</t>
-        </is>
-      </c>
+      <c r="B15" s="61" t="n"/>
       <c r="C15" s="61" t="n"/>
       <c r="D15" s="61" t="n"/>
       <c r="E15" s="61" t="n"/>
       <c r="F15" s="61" t="n"/>
+      <c r="G15" s="61" t="n"/>
+      <c r="H15" s="61" t="n"/>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>REJ-001 a REJ-003 (rejillas de exfiltración)</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="n"/>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="61" t="n"/>
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="n"/>
+      <c r="O15" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="62" t="inlineStr">
@@ -3557,621 +3616,888 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
-    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>2. Condiciones de operación y desempeño</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>2. Condiciones de operación y desempeño</t>
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
-        </is>
-      </c>
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B26" s="59" t="n"/>
+      <c r="C26" s="59" t="n"/>
+      <c r="D26" s="59" t="n"/>
+      <c r="E26" s="59" t="n"/>
+      <c r="F26" s="59" t="n"/>
+      <c r="G26" s="59" t="n"/>
+      <c r="H26" s="59" t="n"/>
+      <c r="I26" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J26" s="59" t="n"/>
+      <c r="K26" s="59" t="n"/>
+      <c r="L26" s="59" t="n"/>
+      <c r="M26" s="59" t="n"/>
+      <c r="N26" s="59" t="n"/>
+      <c r="O26" s="59" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B27" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C27" s="59" t="n"/>
-      <c r="D27" s="59" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="59" t="n"/>
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="n"/>
+      <c r="C27" s="61" t="n"/>
+      <c r="D27" s="61" t="n"/>
+      <c r="E27" s="61" t="n"/>
+      <c r="F27" s="61" t="n"/>
+      <c r="G27" s="61" t="n"/>
+      <c r="H27" s="61" t="n"/>
+      <c r="I27" s="60" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J27" s="61" t="n"/>
+      <c r="K27" s="61" t="n"/>
+      <c r="L27" s="61" t="n"/>
+      <c r="M27" s="61" t="n"/>
+      <c r="N27" s="61" t="n"/>
+      <c r="O27" s="61" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="60" t="inlineStr">
         <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="B28" s="60" t="inlineStr">
-        <is>
-          <t>3 unidades</t>
-        </is>
-      </c>
+          <t>Dimensiones faciales (unitarias)</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="n"/>
       <c r="C28" s="61" t="n"/>
       <c r="D28" s="61" t="n"/>
       <c r="E28" s="61" t="n"/>
       <c r="F28" s="61" t="n"/>
+      <c r="G28" s="61" t="n"/>
+      <c r="H28" s="61" t="n"/>
+      <c r="I28" s="60" t="inlineStr">
+        <is>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
+        </is>
+      </c>
+      <c r="J28" s="61" t="n"/>
+      <c r="K28" s="61" t="n"/>
+      <c r="L28" s="61" t="n"/>
+      <c r="M28" s="61" t="n"/>
+      <c r="N28" s="61" t="n"/>
+      <c r="O28" s="61" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="60" t="inlineStr">
         <is>
-          <t>Dimensiones faciales (unitarias)</t>
-        </is>
-      </c>
-      <c r="B29" s="60" t="inlineStr">
-        <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
-        </is>
-      </c>
+          <t>Caudal total de exfiltración</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="n"/>
       <c r="C29" s="61" t="n"/>
       <c r="D29" s="61" t="n"/>
       <c r="E29" s="61" t="n"/>
       <c r="F29" s="61" t="n"/>
+      <c r="G29" s="61" t="n"/>
+      <c r="H29" s="61" t="n"/>
+      <c r="I29" s="60" t="inlineStr">
+        <is>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
+        </is>
+      </c>
+      <c r="J29" s="61" t="n"/>
+      <c r="K29" s="61" t="n"/>
+      <c r="L29" s="61" t="n"/>
+      <c r="M29" s="61" t="n"/>
+      <c r="N29" s="61" t="n"/>
+      <c r="O29" s="61" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="60" t="inlineStr">
         <is>
-          <t>Caudal total de exfiltración</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="inlineStr">
-        <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
-        </is>
-      </c>
+          <t>Velocidad facial</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="n"/>
       <c r="C30" s="61" t="n"/>
       <c r="D30" s="61" t="n"/>
       <c r="E30" s="61" t="n"/>
       <c r="F30" s="61" t="n"/>
+      <c r="G30" s="61" t="n"/>
+      <c r="H30" s="61" t="n"/>
+      <c r="I30" s="60" t="inlineStr">
+        <is>
+          <t>3 m/s</t>
+        </is>
+      </c>
+      <c r="J30" s="61" t="n"/>
+      <c r="K30" s="61" t="n"/>
+      <c r="L30" s="61" t="n"/>
+      <c r="M30" s="61" t="n"/>
+      <c r="N30" s="61" t="n"/>
+      <c r="O30" s="61" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>Velocidad facial</t>
-        </is>
-      </c>
-      <c r="B31" s="60" t="inlineStr">
-        <is>
-          <t>3 m/s</t>
-        </is>
-      </c>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="n"/>
       <c r="C31" s="61" t="n"/>
       <c r="D31" s="61" t="n"/>
       <c r="E31" s="61" t="n"/>
       <c r="F31" s="61" t="n"/>
+      <c r="G31" s="61" t="n"/>
+      <c r="H31" s="61" t="n"/>
+      <c r="I31" s="60" t="inlineStr">
+        <is>
+          <t>11 Pa</t>
+        </is>
+      </c>
+      <c r="J31" s="61" t="n"/>
+      <c r="K31" s="61" t="n"/>
+      <c r="L31" s="61" t="n"/>
+      <c r="M31" s="61" t="n"/>
+      <c r="N31" s="61" t="n"/>
+      <c r="O31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="60" t="inlineStr">
         <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="inlineStr">
-        <is>
-          <t>11 Pa</t>
-        </is>
-      </c>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="n"/>
       <c r="C32" s="61" t="n"/>
       <c r="D32" s="61" t="n"/>
       <c r="E32" s="61" t="n"/>
       <c r="F32" s="61" t="n"/>
+      <c r="G32" s="61" t="n"/>
+      <c r="H32" s="61" t="n"/>
+      <c r="I32" s="60" t="inlineStr">
+        <is>
+          <t>15 Pa</t>
+        </is>
+      </c>
+      <c r="J32" s="61" t="n"/>
+      <c r="K32" s="61" t="n"/>
+      <c r="L32" s="61" t="n"/>
+      <c r="M32" s="61" t="n"/>
+      <c r="N32" s="61" t="n"/>
+      <c r="O32" s="61" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B33" s="60" t="inlineStr">
-        <is>
-          <t>15 Pa</t>
-        </is>
-      </c>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="n"/>
       <c r="C33" s="61" t="n"/>
       <c r="D33" s="61" t="n"/>
       <c r="E33" s="61" t="n"/>
       <c r="F33" s="61" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="G33" s="61" t="n"/>
+      <c r="H33" s="61" t="n"/>
+      <c r="I33" s="60" t="inlineStr">
         <is>
           <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
-      <c r="C34" s="61" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="61" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+      <c r="J33" s="61" t="n"/>
+      <c r="K33" s="61" t="n"/>
+      <c r="L33" s="61" t="n"/>
+      <c r="M33" s="61" t="n"/>
+      <c r="N33" s="61" t="n"/>
+      <c r="O33" s="61" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="63" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la configuración sin damper de alivio (rejillas a 4 m/s) solo alcanzaría 19.6 Pa de presurización a esta altitud; cerrar el balance a 25 Pa sin damper requeriría un área total de 0.236 m² (0.079 m² por rejilla ≈ 280×281 mm a 4.5 m/s). El sistema adoptado conserva las tres rejillas de 353×336 mm y cierra el balance con el damper barométrico (componente obligatorio; ver HD-INST-001 e informe_investigacion.md §3.2.4).</t>
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
+        <is>
+          <t>3. Construcción y áreas netas</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 2. Especificación constructiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="inlineStr">
+        <is>
+          <t>Característica</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="n"/>
+      <c r="C42" s="59" t="n"/>
+      <c r="D42" s="59" t="n"/>
+      <c r="E42" s="59" t="n"/>
+      <c r="F42" s="59" t="n"/>
+      <c r="G42" s="59" t="n"/>
+      <c r="H42" s="59" t="n"/>
+      <c r="I42" s="59" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J42" s="59" t="n"/>
+      <c r="K42" s="59" t="n"/>
+      <c r="L42" s="59" t="n"/>
+      <c r="M42" s="59" t="n"/>
+      <c r="N42" s="59" t="n"/>
+      <c r="O42" s="59" t="n"/>
+    </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr">
-        <is>
-          <t>3. Construcción y áreas netas</t>
-        </is>
-      </c>
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>Tipo de núcleo</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="61" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="61" t="n"/>
+      <c r="G43" s="61" t="n"/>
+      <c r="H43" s="61" t="n"/>
+      <c r="I43" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+        </is>
+      </c>
+      <c r="J43" s="61" t="n"/>
+      <c r="K43" s="61" t="n"/>
+      <c r="L43" s="61" t="n"/>
+      <c r="M43" s="61" t="n"/>
+      <c r="N43" s="61" t="n"/>
+      <c r="O43" s="61" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 2. Especificación constructiva.</t>
-        </is>
-      </c>
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>Área libre del núcleo</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="n"/>
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="61" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="61" t="n"/>
+      <c r="G44" s="61" t="n"/>
+      <c r="H44" s="61" t="n"/>
+      <c r="I44" s="60" t="inlineStr">
+        <is>
+          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J44" s="61" t="n"/>
+      <c r="K44" s="61" t="n"/>
+      <c r="L44" s="61" t="n"/>
+      <c r="M44" s="61" t="n"/>
+      <c r="N44" s="61" t="n"/>
+      <c r="O44" s="61" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr">
-        <is>
-          <t>Característica</t>
-        </is>
-      </c>
-      <c r="B45" s="59" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="n"/>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
+      <c r="G45" s="61" t="n"/>
+      <c r="H45" s="61" t="n"/>
+      <c r="I45" s="60" t="inlineStr">
+        <is>
+          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
+        </is>
+      </c>
+      <c r="J45" s="61" t="n"/>
+      <c r="K45" s="61" t="n"/>
+      <c r="L45" s="61" t="n"/>
+      <c r="M45" s="61" t="n"/>
+      <c r="N45" s="61" t="n"/>
+      <c r="O45" s="61" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="60" t="inlineStr">
         <is>
-          <t>Tipo de núcleo</t>
-        </is>
-      </c>
-      <c r="B46" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
-        </is>
-      </c>
+          <t>Área neta combinada (núcleo + malla)</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="n"/>
       <c r="C46" s="61" t="n"/>
       <c r="D46" s="61" t="n"/>
       <c r="E46" s="61" t="n"/>
       <c r="F46" s="61" t="n"/>
+      <c r="G46" s="61" t="n"/>
+      <c r="H46" s="61" t="n"/>
+      <c r="I46" s="60" t="inlineStr">
+        <is>
+          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
+        </is>
+      </c>
+      <c r="J46" s="61" t="n"/>
+      <c r="K46" s="61" t="n"/>
+      <c r="L46" s="61" t="n"/>
+      <c r="M46" s="61" t="n"/>
+      <c r="N46" s="61" t="n"/>
+      <c r="O46" s="61" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="60" t="inlineStr">
         <is>
-          <t>Área libre del núcleo</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="inlineStr">
-        <is>
-          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
-        </is>
-      </c>
+          <t>Material de la rejilla</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="n"/>
       <c r="C47" s="61" t="n"/>
       <c r="D47" s="61" t="n"/>
       <c r="E47" s="61" t="n"/>
       <c r="F47" s="61" t="n"/>
+      <c r="G47" s="61" t="n"/>
+      <c r="H47" s="61" t="n"/>
+      <c r="I47" s="60" t="inlineStr">
+        <is>
+          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
+        </is>
+      </c>
+      <c r="J47" s="61" t="n"/>
+      <c r="K47" s="61" t="n"/>
+      <c r="L47" s="61" t="n"/>
+      <c r="M47" s="61" t="n"/>
+      <c r="N47" s="61" t="n"/>
+      <c r="O47" s="61" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="60" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
-        </is>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="n"/>
       <c r="C48" s="61" t="n"/>
       <c r="D48" s="61" t="n"/>
       <c r="E48" s="61" t="n"/>
       <c r="F48" s="61" t="n"/>
+      <c r="G48" s="61" t="n"/>
+      <c r="H48" s="61" t="n"/>
+      <c r="I48" s="60" t="inlineStr">
+        <is>
+          <t>Inox 316</t>
+        </is>
+      </c>
+      <c r="J48" s="61" t="n"/>
+      <c r="K48" s="61" t="n"/>
+      <c r="L48" s="61" t="n"/>
+      <c r="M48" s="61" t="n"/>
+      <c r="N48" s="61" t="n"/>
+      <c r="O48" s="61" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="60" t="inlineStr">
         <is>
-          <t>Área neta combinada (núcleo + malla)</t>
-        </is>
-      </c>
-      <c r="B49" s="60" t="inlineStr">
-        <is>
-          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
-        </is>
-      </c>
+          <t>Montaje de la malla</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="n"/>
       <c r="C49" s="61" t="n"/>
       <c r="D49" s="61" t="n"/>
       <c r="E49" s="61" t="n"/>
       <c r="F49" s="61" t="n"/>
+      <c r="G49" s="61" t="n"/>
+      <c r="H49" s="61" t="n"/>
+      <c r="I49" s="60" t="inlineStr">
+        <is>
+          <t>Marco desmontable para limpieza periódica</t>
+        </is>
+      </c>
+      <c r="J49" s="61" t="n"/>
+      <c r="K49" s="61" t="n"/>
+      <c r="L49" s="61" t="n"/>
+      <c r="M49" s="61" t="n"/>
+      <c r="N49" s="61" t="n"/>
+      <c r="O49" s="61" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="60" t="inlineStr">
         <is>
-          <t>Material de la rejilla</t>
-        </is>
-      </c>
-      <c r="B50" s="60" t="inlineStr">
-        <is>
-          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
-        </is>
-      </c>
+          <t>Par galvánico</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="n"/>
       <c r="C50" s="61" t="n"/>
       <c r="D50" s="61" t="n"/>
       <c r="E50" s="61" t="n"/>
       <c r="F50" s="61" t="n"/>
+      <c r="G50" s="61" t="n"/>
+      <c r="H50" s="61" t="n"/>
+      <c r="I50" s="60" t="inlineStr">
+        <is>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
+        </is>
+      </c>
+      <c r="J50" s="61" t="n"/>
+      <c r="K50" s="61" t="n"/>
+      <c r="L50" s="61" t="n"/>
+      <c r="M50" s="61" t="n"/>
+      <c r="N50" s="61" t="n"/>
+      <c r="O50" s="61" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="60" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="B51" s="60" t="inlineStr">
-        <is>
-          <t>Inox 316</t>
-        </is>
-      </c>
+          <t>Ensayo de desempeño</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="n"/>
       <c r="C51" s="61" t="n"/>
       <c r="D51" s="61" t="n"/>
       <c r="E51" s="61" t="n"/>
       <c r="F51" s="61" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="60" t="inlineStr">
-        <is>
-          <t>Montaje de la malla</t>
-        </is>
-      </c>
-      <c r="B52" s="60" t="inlineStr">
-        <is>
-          <t>Marco desmontable para limpieza periódica</t>
-        </is>
-      </c>
-      <c r="C52" s="61" t="n"/>
-      <c r="D52" s="61" t="n"/>
-      <c r="E52" s="61" t="n"/>
-      <c r="F52" s="61" t="n"/>
+      <c r="G51" s="61" t="n"/>
+      <c r="H51" s="61" t="n"/>
+      <c r="I51" s="60" t="inlineStr">
+        <is>
+          <t>ASHRAE 70 (medición de rejillas)</t>
+        </is>
+      </c>
+      <c r="J51" s="61" t="n"/>
+      <c r="K51" s="61" t="n"/>
+      <c r="L51" s="61" t="n"/>
+      <c r="M51" s="61" t="n"/>
+      <c r="N51" s="61" t="n"/>
+      <c r="O51" s="61" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr">
-        <is>
-          <t>Par galvánico</t>
-        </is>
-      </c>
-      <c r="B53" s="60" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="C53" s="61" t="n"/>
-      <c r="D53" s="61" t="n"/>
-      <c r="E53" s="61" t="n"/>
-      <c r="F53" s="61" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="60" t="inlineStr">
-        <is>
-          <t>Ensayo de desempeño</t>
-        </is>
-      </c>
-      <c r="B54" s="60" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="C54" s="61" t="n"/>
-      <c r="D54" s="61" t="n"/>
-      <c r="E54" s="61" t="n"/>
-      <c r="F54" s="61" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="63" t="inlineStr">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
+        <is>
+          <t>4. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B59" s="59" t="n"/>
+      <c r="C59" s="59" t="n"/>
+      <c r="D59" s="59" t="inlineStr">
+        <is>
+          <t>Tipo / material</t>
+        </is>
+      </c>
+      <c r="E59" s="59" t="n"/>
+      <c r="F59" s="59" t="n"/>
+      <c r="G59" s="59" t="inlineStr">
+        <is>
+          <t>Pros</t>
+        </is>
+      </c>
+      <c r="H59" s="59" t="n"/>
+      <c r="I59" s="59" t="n"/>
+      <c r="J59" s="59" t="inlineStr">
+        <is>
+          <t>Contras</t>
+        </is>
+      </c>
+      <c r="K59" s="59" t="n"/>
+      <c r="L59" s="59" t="n"/>
+      <c r="M59" s="59" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N59" s="59" t="n"/>
+      <c r="O59" s="59" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F / 50R</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="n"/>
+      <c r="C60" s="61" t="n"/>
+      <c r="D60" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="n"/>
+      <c r="F60" s="61" t="n"/>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
+      <c r="H60" s="61" t="n"/>
+      <c r="I60" s="61" t="n"/>
+      <c r="J60" s="60" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
+      <c r="K60" s="61" t="n"/>
+      <c r="L60" s="61" t="n"/>
+      <c r="M60" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
+      <c r="N60" s="61" t="n"/>
+      <c r="O60" s="61" t="n"/>
+    </row>
     <row r="61">
-      <c r="A61" s="62" t="inlineStr">
-        <is>
-          <t>4. Candidatos comerciales</t>
-        </is>
-      </c>
+      <c r="A61" s="60" t="inlineStr">
+        <is>
+          <t>Krueger EGC5</t>
+        </is>
+      </c>
+      <c r="B61" s="61" t="n"/>
+      <c r="C61" s="61" t="n"/>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="61" t="n"/>
+      <c r="G61" s="60" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
+      <c r="H61" s="61" t="n"/>
+      <c r="I61" s="61" t="n"/>
+      <c r="J61" s="60" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
+      <c r="K61" s="61" t="n"/>
+      <c r="L61" s="61" t="n"/>
+      <c r="M61" s="60" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
+      <c r="N61" s="61" t="n"/>
+      <c r="O61" s="61" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
+      <c r="A62" s="60" t="inlineStr">
+        <is>
+          <t>ProAire S.A.S (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B62" s="61" t="n"/>
+      <c r="C62" s="61" t="n"/>
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>Fabricación a medida con corte láser, inox 316</t>
+        </is>
+      </c>
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="61" t="n"/>
+      <c r="G62" s="60" t="inlineStr">
+        <is>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+        </is>
+      </c>
+      <c r="H62" s="61" t="n"/>
+      <c r="I62" s="61" t="n"/>
+      <c r="J62" s="60" t="inlineStr">
+        <is>
+          <t>Submittal y Ak por confirmar con proveedor</t>
+        </is>
+      </c>
+      <c r="K62" s="61" t="n"/>
+      <c r="L62" s="61" t="n"/>
+      <c r="M62" s="60" t="inlineStr">
+        <is>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+        </is>
+      </c>
+      <c r="N62" s="61" t="n"/>
+      <c r="O62" s="61" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="59" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B63" s="59" t="inlineStr">
-        <is>
-          <t>Tipo / material</t>
-        </is>
-      </c>
-      <c r="C63" s="59" t="inlineStr">
-        <is>
-          <t>Pros</t>
-        </is>
-      </c>
-      <c r="D63" s="59" t="inlineStr">
-        <is>
-          <t>Contras</t>
-        </is>
-      </c>
-      <c r="E63" s="59" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="F63" s="59" t="n"/>
+      <c r="A63" s="60" t="inlineStr">
+        <is>
+          <t>Laminaire (Colombia)</t>
+        </is>
+      </c>
+      <c r="B63" s="61" t="n"/>
+      <c r="C63" s="61" t="n"/>
+      <c r="D63" s="60" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores en aluminio a pedido</t>
+        </is>
+      </c>
+      <c r="E63" s="61" t="n"/>
+      <c r="F63" s="61" t="n"/>
+      <c r="G63" s="60" t="inlineStr">
+        <is>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
+        </is>
+      </c>
+      <c r="H63" s="61" t="n"/>
+      <c r="I63" s="61" t="n"/>
+      <c r="J63" s="60" t="inlineStr">
+        <is>
+          <t>Confirmar ejecución inox</t>
+        </is>
+      </c>
+      <c r="K63" s="61" t="n"/>
+      <c r="L63" s="61" t="n"/>
+      <c r="M63" s="60" t="inlineStr">
+        <is>
+          <t>laminaire.net (https://laminaire.net/)</t>
+        </is>
+      </c>
+      <c r="N63" s="61" t="n"/>
+      <c r="O63" s="61" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="60" t="inlineStr">
         <is>
-          <t>Titus 50F / 50R</t>
-        </is>
-      </c>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
-        </is>
-      </c>
-      <c r="C64" s="60" t="inlineStr">
-        <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
-        </is>
-      </c>
+          <t>CL Ingeniería (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="n"/>
+      <c r="C64" s="61" t="n"/>
       <c r="D64" s="60" t="inlineStr">
         <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
-        </is>
-      </c>
-      <c r="E64" s="60" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
-        </is>
-      </c>
+          <t>Rejillas, dampers y accesorios HVAC</t>
+        </is>
+      </c>
+      <c r="E64" s="61" t="n"/>
       <c r="F64" s="61" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="60" t="inlineStr">
-        <is>
-          <t>Krueger EGC5</t>
-        </is>
-      </c>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio</t>
-        </is>
-      </c>
-      <c r="C65" s="60" t="inlineStr">
-        <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
-        </is>
-      </c>
-      <c r="D65" s="60" t="inlineStr">
-        <is>
-          <t>Sin ejecución inox</t>
-        </is>
-      </c>
-      <c r="E65" s="60" t="inlineStr">
-        <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
-        </is>
-      </c>
-      <c r="F65" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="60" t="inlineStr">
-        <is>
-          <t>ProAire S.A.S (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B66" s="60" t="inlineStr">
-        <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
-        </is>
-      </c>
-      <c r="C66" s="60" t="inlineStr">
-        <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
-        </is>
-      </c>
-      <c r="D66" s="60" t="inlineStr">
-        <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="E66" s="60" t="inlineStr">
-        <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="F66" s="61" t="n"/>
+      <c r="G64" s="60" t="inlineStr">
+        <is>
+          <t>Canal local adicional</t>
+        </is>
+      </c>
+      <c r="H64" s="61" t="n"/>
+      <c r="I64" s="61" t="n"/>
+      <c r="J64" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo genérico</t>
+        </is>
+      </c>
+      <c r="K64" s="61" t="n"/>
+      <c r="L64" s="61" t="n"/>
+      <c r="M64" s="60" t="inlineStr">
+        <is>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
+        </is>
+      </c>
+      <c r="N64" s="61" t="n"/>
+      <c r="O64" s="61" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="60" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B67" s="60" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="C67" s="60" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="D67" s="60" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="E67" s="60" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="F67" s="61" t="n"/>
+      <c r="A67" s="62" t="inlineStr">
+        <is>
+          <t>5. Instalación</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="60" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B68" s="60" t="inlineStr">
-        <is>
-          <t>Rejillas, dampers y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="C68" s="60" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="D68" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="E68" s="60" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="F68" s="61" t="n"/>
-    </row>
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
-      <c r="A71" s="62" t="inlineStr">
-        <is>
-          <t>5. Instalación</t>
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="63" t="inlineStr">
         <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4). 5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta. 5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
+          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="62" t="inlineStr">
+        <is>
+          <t>6. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
+        <is>
+          <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
+        </is>
+      </c>
+    </row>
     <row r="76"/>
     <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="81">
-      <c r="A81" s="62" t="inlineStr">
-        <is>
-          <t>6. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="63" t="inlineStr">
-        <is>
-          <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="A82:F86"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="E68:F68"/>
+  <mergeCells count="101">
+    <mergeCell ref="I44:O44"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A19:O22"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A35:O38"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="I46:O46"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A67:O67"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="I43:O43"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="I50:O50"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="I45:O45"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="I47:O47"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="A72:F79"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A36:F41"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A56:F59"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="I51:O51"/>
+    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="M61:O61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="I49:O49"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A53:O55"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A9:O9"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A19:F23"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="M59:O59"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="M60:O60"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I48:O48"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A75:O77"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A57:O57"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="M63:O63"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="A68:O70"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="D63:F63"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="I42:O42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
